--- a/data/warn-scraper/cache/ia/source.xlsx
+++ b/data/warn-scraper/cache/ia/source.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iowamac.sharepoint.com/sites/IWDWorkforceServices/Shared Documents/Rapid Response/WARN/WARN Log/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{769AC9C2-A5FB-4545-850B-FDD2B89876A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A9D01BB-2B14-4BE9-87E9-5336E1D17FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,12 +46,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6862" uniqueCount="1197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6861" uniqueCount="1195">
   <si>
     <t>Iowa WARN Log</t>
   </si>
   <si>
-    <t>Updated: 09-02-2026</t>
+    <t>Updated: 09-16-2026</t>
   </si>
   <si>
     <t>Company</t>
@@ -3549,64 +3549,58 @@
     <t>12/20/2022</t>
   </si>
   <si>
+    <t>1323 Northeast Ave</t>
+  </si>
+  <si>
+    <t>09/23/2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health Care and Social Assistance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHEP Services, LLC </t>
+  </si>
+  <si>
+    <t>10950 High Life Court SW</t>
+  </si>
+  <si>
+    <t>10/06/2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Estate adn Rental and Leasing </t>
+  </si>
+  <si>
+    <t>Sequel Youth Services of Forest Ridge Youth Services, LLC</t>
+  </si>
+  <si>
+    <t>200 6th Street</t>
+  </si>
+  <si>
+    <t>Estherville</t>
+  </si>
+  <si>
+    <t>Emmet</t>
+  </si>
+  <si>
+    <t>10/12/2021</t>
+  </si>
+  <si>
+    <t>TPI Composites</t>
+  </si>
+  <si>
+    <t>2300 N 33rd E</t>
+  </si>
+  <si>
+    <t>10/18/2021</t>
+  </si>
+  <si>
+    <t>ABB Inc</t>
+  </si>
+  <si>
+    <t>510 East Agency Road</t>
+  </si>
+  <si>
     <t xml:space="preserve">Principal Life Insurance Company </t>
-  </si>
-  <si>
-    <t xml:space="preserve">711 High Street </t>
-  </si>
-  <si>
-    <t>9/9/2021</t>
-  </si>
-  <si>
-    <t>1323 Northeast Ave</t>
-  </si>
-  <si>
-    <t>09/23/2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health Care and Social Assistance </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHEP Services, LLC </t>
-  </si>
-  <si>
-    <t>10950 High Life Court SW</t>
-  </si>
-  <si>
-    <t>10/06/2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Estate adn Rental and Leasing </t>
-  </si>
-  <si>
-    <t>Sequel Youth Services of Forest Ridge Youth Services, LLC</t>
-  </si>
-  <si>
-    <t>200 6th Street</t>
-  </si>
-  <si>
-    <t>Estherville</t>
-  </si>
-  <si>
-    <t>Emmet</t>
-  </si>
-  <si>
-    <t>10/12/2021</t>
-  </si>
-  <si>
-    <t>TPI Composites</t>
-  </si>
-  <si>
-    <t>2300 N 33rd E</t>
-  </si>
-  <si>
-    <t>10/18/2021</t>
-  </si>
-  <si>
-    <t>ABB Inc</t>
-  </si>
-  <si>
-    <t>510 East Agency Road</t>
   </si>
   <si>
     <t>711 High Street</t>
@@ -5589,8 +5583,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L94" totalsRowShown="0" headerRowDxfId="77">
-  <autoFilter ref="A2:L94" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L95" totalsRowShown="0" headerRowDxfId="77">
+  <autoFilter ref="A2:L95" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{624CA823-360D-451E-81B4-66E6AEBB7049}" name="Company" dataDxfId="76"/>
     <tableColumn id="2" xr3:uid="{2CB99E09-68C4-4CD3-8D8C-07722FD0C438}" name="Address Line 1" dataDxfId="75"/>
@@ -5694,8 +5688,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1BEA32C5-692B-4A99-ADCC-E13692B74419}" name="Table413" displayName="Table413" ref="A2:L9" totalsRowShown="0" headerRowDxfId="12">
-  <autoFilter ref="A2:L9" xr:uid="{7470B6DE-4503-4D23-8D41-AC272013CBFF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1BEA32C5-692B-4A99-ADCC-E13692B74419}" name="Table413" displayName="Table413" ref="A2:L8" totalsRowShown="0" headerRowDxfId="12">
+  <autoFilter ref="A2:L8" xr:uid="{7470B6DE-4503-4D23-8D41-AC272013CBFF}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{5EC3C567-DD83-4D25-83FC-574F4BD72715}" name="Company" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{584A3774-9FF7-45FB-94BD-71E440D87D86}" name="Address Line 1" dataDxfId="10"/>
@@ -5912,7 +5906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.5" style="13" customWidth="1"/>
@@ -9480,6 +9474,44 @@
         <v>27</v>
       </c>
       <c r="L94" s="76" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="15" customHeight="1">
+      <c r="A95" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="B95" s="76" t="s">
+        <v>138</v>
+      </c>
+      <c r="C95" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="D95" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="E95" s="76" t="s">
+        <v>18</v>
+      </c>
+      <c r="F95" s="77">
+        <v>50266</v>
+      </c>
+      <c r="G95" s="76" t="s">
+        <v>142</v>
+      </c>
+      <c r="H95" s="77">
+        <v>35</v>
+      </c>
+      <c r="I95" s="78">
+        <v>46280</v>
+      </c>
+      <c r="J95" s="78">
+        <v>46340</v>
+      </c>
+      <c r="K95" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="L95" s="76" t="s">
         <v>28</v>
       </c>
     </row>
@@ -29094,7 +29126,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC2664FB-EEE5-4B9D-9CD3-D928A6EDFE7A}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="38.5" style="13" customWidth="1"/>
@@ -29167,154 +29199,154 @@
     </row>
     <row r="3" spans="1:12" ht="15">
       <c r="A3" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>1167</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>1168</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>17</v>
+        <v>269</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>25</v>
+        <v>270</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="5">
-        <v>50392</v>
+        <v>50010</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="J3" s="8">
-        <v>44480</v>
+        <v>44491</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>28</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15">
       <c r="A4" s="6" t="s">
-        <v>241</v>
+        <v>1170</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>269</v>
+        <v>137</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>270</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="5">
-        <v>50010</v>
+        <v>52404</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H4" s="5">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="J4" s="8">
-        <v>44491</v>
+        <v>44535</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>27</v>
+        <v>233</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="15">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="30">
       <c r="A5" s="6" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>137</v>
+        <v>1176</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>76</v>
+        <v>1177</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="5">
-        <v>52404</v>
+        <v>51334</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H5" s="5">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="J5" s="8">
-        <v>44535</v>
+        <v>44505</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>233</v>
+        <v>1003</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="30">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15">
       <c r="A6" s="6" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1179</v>
+        <v>656</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1180</v>
+        <v>657</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="5">
-        <v>51334</v>
+        <v>50208</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="H6" s="5">
-        <v>59</v>
+        <v>710</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>1181</v>
       </c>
       <c r="J6" s="8">
-        <v>44505</v>
+        <v>44561</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>1003</v>
+        <v>27</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>1172</v>
+        <v>984</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15">
@@ -29325,109 +29357,71 @@
         <v>1183</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>656</v>
+        <v>332</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>657</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="5">
-        <v>50208</v>
+        <v>52655</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>19</v>
+        <v>532</v>
       </c>
       <c r="H7" s="5">
-        <v>710</v>
+        <v>247</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="J7" s="8">
-        <v>44561</v>
+        <v>44547</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>984</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15">
       <c r="A8" s="6" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>1185</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>1186</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>332</v>
+        <v>381</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="F8" s="5">
-        <v>52655</v>
+        <v>50392</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>532</v>
       </c>
       <c r="H8" s="5">
-        <v>247</v>
+        <v>30</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="J8" s="8">
-        <v>44547</v>
+        <v>44519</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15">
-      <c r="A9" s="6" t="s">
-        <v>1167</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1187</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" s="5">
-        <v>50392</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="H9" s="5">
-        <v>30</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>1188</v>
-      </c>
-      <c r="J9" s="8">
-        <v>44519</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" s="2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -29924,7 +29918,7 @@
         <v>392</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>18</v>
@@ -30222,7 +30216,7 @@
         <v>515</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>712</v>
@@ -30260,7 +30254,7 @@
         <v>588</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>664</v>
@@ -31134,7 +31128,7 @@
         <v>209</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>211</v>
@@ -31172,7 +31166,7 @@
         <v>209</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>211</v>
@@ -31514,7 +31508,7 @@
         <v>430</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="C56" s="34" t="s">
         <v>56</v>
@@ -32233,7 +32227,7 @@
     </row>
     <row r="75" spans="1:12" ht="15">
       <c r="A75" s="11" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>663</v>
@@ -32464,7 +32458,7 @@
         <v>745</v>
       </c>
       <c r="B81" s="34" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="C81" s="34" t="s">
         <v>747</v>
@@ -36587,34 +36581,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="465031c5-3d91-457d-a71b-eb9b5941244d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="bb079858-90af-4c1d-b6f1-55332f11d181" xsi:nil="true"/>
-    <SharedWithUsers xmlns="bb079858-90af-4c1d-b6f1-55332f11d181">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <MediaLengthInSeconds xmlns="465031c5-3d91-457d-a71b-eb9b5941244d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008FFDA55EC64F6340997887DF003F4858" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="610c4182e7e7902e7aea694cdd9432aa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb079858-90af-4c1d-b6f1-55332f11d181" xmlns:ns3="465031c5-3d91-457d-a71b-eb9b5941244d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="92492927522a77c15d270bbe3d3d4b37" ns2:_="" ns3:_="">
     <xsd:import namespace="bb079858-90af-4c1d-b6f1-55332f11d181"/>
@@ -36849,8 +36815,36 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="465031c5-3d91-457d-a71b-eb9b5941244d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="bb079858-90af-4c1d-b6f1-55332f11d181" xsi:nil="true"/>
+    <SharedWithUsers xmlns="bb079858-90af-4c1d-b6f1-55332f11d181">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <MediaLengthInSeconds xmlns="465031c5-3d91-457d-a71b-eb9b5941244d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D66E9BA-12AB-4417-9A6A-6113397F4F5F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6492E40-AF0B-480F-B23D-6DA53B2EBE0E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -36858,5 +36852,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6492E40-AF0B-480F-B23D-6DA53B2EBE0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D66E9BA-12AB-4417-9A6A-6113397F4F5F}"/>
 </file>
--- a/data/warn-scraper/cache/ia/source.xlsx
+++ b/data/warn-scraper/cache/ia/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iowamac.sharepoint.com/sites/IWDWorkforceServices/Shared Documents/Rapid Response/WARN/WARN Log/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A9D01BB-2B14-4BE9-87E9-5336E1D17FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E72FC84-BFF5-48B3-9976-A854DD665330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,12 +46,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6861" uniqueCount="1195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6869" uniqueCount="1195">
   <si>
     <t>Iowa WARN Log</t>
   </si>
   <si>
-    <t>Updated: 09-16-2026</t>
+    <t>Updated: 09-22-2026</t>
   </si>
   <si>
     <t>Company</t>
@@ -3775,7 +3775,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -3835,11 +3835,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4068,6 +4081,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -5583,8 +5605,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L95" totalsRowShown="0" headerRowDxfId="77">
-  <autoFilter ref="A2:L95" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L96" totalsRowShown="0" headerRowDxfId="77">
+  <autoFilter ref="A2:L96" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{624CA823-360D-451E-81B4-66E6AEBB7049}" name="Company" dataDxfId="76"/>
     <tableColumn id="2" xr3:uid="{2CB99E09-68C4-4CD3-8D8C-07722FD0C438}" name="Address Line 1" dataDxfId="75"/>
@@ -5906,7 +5928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.5" style="13" customWidth="1"/>
@@ -9513,6 +9535,44 @@
       </c>
       <c r="L95" s="76" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="15" customHeight="1">
+      <c r="A96" s="80" t="s">
+        <v>180</v>
+      </c>
+      <c r="B96" s="88" t="s">
+        <v>181</v>
+      </c>
+      <c r="C96" s="88" t="s">
+        <v>137</v>
+      </c>
+      <c r="D96" s="88" t="s">
+        <v>76</v>
+      </c>
+      <c r="E96" s="88" t="s">
+        <v>18</v>
+      </c>
+      <c r="F96" s="89">
+        <v>52498</v>
+      </c>
+      <c r="G96" s="88" t="s">
+        <v>67</v>
+      </c>
+      <c r="H96" s="89">
+        <v>1</v>
+      </c>
+      <c r="I96" s="90">
+        <v>46287</v>
+      </c>
+      <c r="J96" s="90">
+        <v>46325</v>
+      </c>
+      <c r="K96" s="88" t="s">
+        <v>64</v>
+      </c>
+      <c r="L96" s="88" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -36581,6 +36641,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008FFDA55EC64F6340997887DF003F4858" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="610c4182e7e7902e7aea694cdd9432aa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb079858-90af-4c1d-b6f1-55332f11d181" xmlns:ns3="465031c5-3d91-457d-a71b-eb9b5941244d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="92492927522a77c15d270bbe3d3d4b37" ns2:_="" ns3:_="">
     <xsd:import namespace="bb079858-90af-4c1d-b6f1-55332f11d181"/>
@@ -36815,15 +36884,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -36844,11 +36904,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6492E40-AF0B-480F-B23D-6DA53B2EBE0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F40177C-67A3-4DD8-A168-9BC85606FD5C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F40177C-67A3-4DD8-A168-9BC85606FD5C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6492E40-AF0B-480F-B23D-6DA53B2EBE0E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/warn-scraper/cache/ia/source.xlsx
+++ b/data/warn-scraper/cache/ia/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iowamac.sharepoint.com/sites/IWDWorkforceServices/Shared Documents/Rapid Response/WARN/WARN Log/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46B87C3F-D930-4AE1-AC79-83703893D2AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FA6D925-1C9B-424C-905B-832B6A2DFD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -46,12 +46,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6876" uniqueCount="1197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6863" uniqueCount="1193">
   <si>
     <t>Iowa WARN Log</t>
   </si>
   <si>
-    <t>Updated: 10-1-2026</t>
+    <t>Updated: 10-9-2026</t>
   </si>
   <si>
     <t>Company</t>
@@ -3559,18 +3559,6 @@
   </si>
   <si>
     <t>12/20/2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHEP Services, LLC </t>
-  </si>
-  <si>
-    <t>10950 High Life Court SW</t>
-  </si>
-  <si>
-    <t>10/06/2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Estate adn Rental and Leasing </t>
   </si>
   <si>
     <t>Sequel Youth Services of Forest Ridge Youth Services, LLC</t>
@@ -3749,7 +3737,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3772,12 +3760,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
         <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor theme="0" tint="-0.14999847407452621"/>
       </patternFill>
     </fill>
   </fills>
@@ -3858,7 +3840,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4075,18 +4057,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5612,8 +5582,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L98" totalsRowShown="0" headerRowDxfId="77">
-  <autoFilter ref="A2:L98" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L99" totalsRowShown="0" headerRowDxfId="77">
+  <autoFilter ref="A2:L99" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{624CA823-360D-451E-81B4-66E6AEBB7049}" name="Company" dataDxfId="76"/>
     <tableColumn id="2" xr3:uid="{2CB99E09-68C4-4CD3-8D8C-07722FD0C438}" name="Address Line 1" dataDxfId="75"/>
@@ -5633,8 +5603,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C38DC0A3-5963-41DA-B1AE-851C8651B8D6}" name="Table49" displayName="Table49" ref="A2:L192" totalsRowShown="0" headerRowDxfId="64">
-  <autoFilter ref="A2:L192" xr:uid="{9A8EC2A9-F654-4ECE-92B0-473AB61146BD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C38DC0A3-5963-41DA-B1AE-851C8651B8D6}" name="Table49" displayName="Table49" ref="A2:L191" totalsRowShown="0" headerRowDxfId="64">
+  <autoFilter ref="A2:L191" xr:uid="{9A8EC2A9-F654-4ECE-92B0-473AB61146BD}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{F47EFFBD-8370-4B50-94FC-3C9E4F1AE434}" name="Company" dataDxfId="63"/>
     <tableColumn id="2" xr3:uid="{93297EE1-63D9-44D4-B13B-2B74D5923198}" name="Address Line 1" dataDxfId="62"/>
@@ -5717,8 +5687,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1BEA32C5-692B-4A99-ADCC-E13692B74419}" name="Table413" displayName="Table413" ref="A2:L7" totalsRowShown="0" headerRowDxfId="12">
-  <autoFilter ref="A2:L7" xr:uid="{7470B6DE-4503-4D23-8D41-AC272013CBFF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1BEA32C5-692B-4A99-ADCC-E13692B74419}" name="Table413" displayName="Table413" ref="A2:L6" totalsRowShown="0" headerRowDxfId="12">
+  <autoFilter ref="A2:L6" xr:uid="{7470B6DE-4503-4D23-8D41-AC272013CBFF}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{5EC3C567-DD83-4D25-83FC-574F4BD72715}" name="Company" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{584A3774-9FF7-45FB-94BD-71E440D87D86}" name="Address Line 1" dataDxfId="10"/>
@@ -5935,7 +5905,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.5" style="13" customWidth="1"/>
@@ -9548,37 +9518,37 @@
       <c r="A96" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="B96" s="88" t="s">
+      <c r="B96" s="84" t="s">
         <v>181</v>
       </c>
-      <c r="C96" s="88" t="s">
+      <c r="C96" s="84" t="s">
         <v>137</v>
       </c>
-      <c r="D96" s="88" t="s">
+      <c r="D96" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="E96" s="88" t="s">
+      <c r="E96" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="F96" s="89">
+      <c r="F96" s="85">
         <v>52498</v>
       </c>
-      <c r="G96" s="88" t="s">
+      <c r="G96" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="H96" s="89">
+      <c r="H96" s="85">
         <v>1</v>
       </c>
-      <c r="I96" s="90">
+      <c r="I96" s="86">
         <v>46287</v>
       </c>
-      <c r="J96" s="90">
+      <c r="J96" s="86">
         <v>46325</v>
       </c>
-      <c r="K96" s="88" t="s">
+      <c r="K96" s="84" t="s">
         <v>64</v>
       </c>
-      <c r="L96" s="88" t="s">
+      <c r="L96" s="84" t="s">
         <v>182</v>
       </c>
     </row>
@@ -9654,7 +9624,45 @@
       <c r="K98" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="L98" s="91" t="s">
+      <c r="L98" s="87" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="15" customHeight="1">
+      <c r="A99" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F99" s="5">
+        <v>50436</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H99" s="5">
+        <v>51</v>
+      </c>
+      <c r="I99" s="22">
+        <v>46304</v>
+      </c>
+      <c r="J99" s="22">
+        <v>46335</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L99" s="2" t="s">
         <v>179</v>
       </c>
     </row>
@@ -9679,7 +9687,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E1DDF6-6CC3-48B9-A90E-CA11C6F8439A}">
-  <dimension ref="A1:L194"/>
+  <dimension ref="A1:L192"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="38.5" style="13" customWidth="1"/>
@@ -16932,106 +16940,42 @@
         <v>58</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="2.25" customHeight="1">
-      <c r="A192" s="6"/>
-      <c r="B192" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D192" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F192" s="5">
-        <v>51106</v>
-      </c>
-      <c r="G192" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H192" s="5">
-        <v>50</v>
-      </c>
-      <c r="I192" s="22"/>
-      <c r="J192" s="22"/>
-      <c r="K192" s="2"/>
-      <c r="L192" s="2"/>
-    </row>
-    <row r="193" spans="1:12" ht="15">
-      <c r="A193" s="80" t="s">
+    <row r="192" spans="1:12" ht="15">
+      <c r="A192" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="B193" s="81" t="s">
+      <c r="B192" s="81" t="s">
         <v>181</v>
       </c>
-      <c r="C193" s="81" t="s">
+      <c r="C192" s="81" t="s">
         <v>137</v>
       </c>
-      <c r="D193" s="81" t="s">
+      <c r="D192" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="E193" s="81" t="s">
+      <c r="E192" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="F193" s="82">
+      <c r="F192" s="82">
         <v>52498</v>
       </c>
-      <c r="G193" s="81" t="s">
+      <c r="G192" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="H193" s="82">
+      <c r="H192" s="82">
         <v>1</v>
       </c>
-      <c r="I193" s="83">
+      <c r="I192" s="83">
         <v>46259</v>
       </c>
-      <c r="J193" s="83">
+      <c r="J192" s="83">
         <v>46295</v>
       </c>
-      <c r="K193" s="81" t="s">
+      <c r="K192" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="L193" s="81" t="s">
+      <c r="L192" s="81" t="s">
         <v>182</v>
-      </c>
-    </row>
-    <row r="194" spans="1:12" ht="2.25" customHeight="1">
-      <c r="A194" s="84"/>
-      <c r="B194" s="85" t="s">
-        <v>161</v>
-      </c>
-      <c r="C194" s="85" t="s">
-        <v>88</v>
-      </c>
-      <c r="D194" s="85" t="s">
-        <v>89</v>
-      </c>
-      <c r="E194" s="85" t="s">
-        <v>63</v>
-      </c>
-      <c r="F194" s="86">
-        <v>50644</v>
-      </c>
-      <c r="G194" s="85" t="s">
-        <v>142</v>
-      </c>
-      <c r="H194" s="86">
-        <v>5</v>
-      </c>
-      <c r="I194" s="87">
-        <v>46265</v>
-      </c>
-      <c r="J194" s="87">
-        <v>46265</v>
-      </c>
-      <c r="K194" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="L194" s="85" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -29269,7 +29213,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC2664FB-EEE5-4B9D-9CD3-D928A6EDFE7A}">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="38.5" style="13" customWidth="1"/>
@@ -29340,7 +29284,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15">
+    <row r="3" spans="1:12" ht="30">
       <c r="A3" s="6" t="s">
         <v>1171</v>
       </c>
@@ -29348,185 +29292,147 @@
         <v>1172</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>137</v>
+        <v>1173</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>76</v>
+        <v>1174</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="5">
-        <v>52404</v>
+        <v>51334</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H3" s="5">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="J3" s="8">
-        <v>44535</v>
+        <v>44505</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>237</v>
+        <v>1007</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="30">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15">
       <c r="A4" s="6" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1177</v>
+        <v>660</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1178</v>
+        <v>661</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="5">
-        <v>51334</v>
+        <v>50208</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="H4" s="5">
-        <v>59</v>
+        <v>710</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>1179</v>
       </c>
       <c r="J4" s="8">
-        <v>44505</v>
+        <v>44561</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>1007</v>
+        <v>27</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1180</v>
+        <v>988</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15">
       <c r="A5" s="6" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>1181</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>1182</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>660</v>
+        <v>336</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>661</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="5">
-        <v>50208</v>
+        <v>52655</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>19</v>
+        <v>536</v>
       </c>
       <c r="H5" s="5">
-        <v>710</v>
+        <v>247</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="J5" s="8">
-        <v>44561</v>
+        <v>44547</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>988</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15">
       <c r="A6" s="6" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>336</v>
+        <v>385</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="F6" s="5">
-        <v>52655</v>
+        <v>50392</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>536</v>
       </c>
       <c r="H6" s="5">
-        <v>247</v>
+        <v>30</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="J6" s="8">
-        <v>44547</v>
+        <v>44519</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15">
-      <c r="A7" s="6" t="s">
-        <v>1186</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1187</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="5">
-        <v>50392</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="H7" s="5">
-        <v>30</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>1188</v>
-      </c>
-      <c r="J7" s="8">
-        <v>44519</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -30023,7 +29929,7 @@
         <v>396</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>18</v>
@@ -30321,7 +30227,7 @@
         <v>519</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>716</v>
@@ -30359,7 +30265,7 @@
         <v>592</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>668</v>
@@ -31233,7 +31139,7 @@
         <v>213</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>215</v>
@@ -31271,7 +31177,7 @@
         <v>213</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>215</v>
@@ -31613,7 +31519,7 @@
         <v>434</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="C56" s="34" t="s">
         <v>56</v>
@@ -32332,7 +32238,7 @@
     </row>
     <row r="75" spans="1:12" ht="15">
       <c r="A75" s="11" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>667</v>
@@ -32563,7 +32469,7 @@
         <v>749</v>
       </c>
       <c r="B81" s="34" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="C81" s="34" t="s">
         <v>751</v>
